--- a/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate2/gate2_qualitative_patterns.xlsx
+++ b/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate2/gate2_qualitative_patterns.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Kotlin の sksamuel/scrimage ライブラリで、画像上に文字列を描画し、文字列の縁取りをするコードを生成してください。文字の色は白、縁は黒で描画します。</t>
+          <t>Using Kotlin with the sksamuel/scrimage library, generate code to draw text on an image with an outline. Render white text with a black border.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
